--- a/Side Bar Files/GWD Data/PVC Fittings PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC Fittings PRICE.xlsx
@@ -610,9 +610,15 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -682,14 +688,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -699,7 +709,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1114,7 +1126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84323A27-C2FA-4317-98ED-047923A9B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89095139-CD5F-479B-9B98-FC816F38B9A7}">
   <dimension ref="A1:G728"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC Fittings PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC Fittings PRICE.xlsx
@@ -399,6 +399,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color rgb="FF212529"/>
       <name val="Cambria"/>
@@ -414,12 +420,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Cambria"/>
       <family val="2"/>
@@ -577,32 +577,18 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -622,58 +608,58 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -685,71 +671,74 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -1126,7 +1115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89095139-CD5F-479B-9B98-FC816F38B9A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BC0C00-BA7F-4CDD-B6B4-44BBEC52BAA6}">
   <dimension ref="A1:G728"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
@@ -12254,7 +12243,7 @@
         <f>F724+F723</f>
         <v>28.949024000000001</v>
       </c>
-      <c r="G725" s="15"/>
+      <c r="G725" s="47"/>
     </row>
     <row r="726" spans="1:7" ht="12.75">
       <c r="A726" s="16" t="s">

--- a/Side Bar Files/GWD Data/PVC Fittings PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC Fittings PRICE.xlsx
@@ -1115,7 +1115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BC0C00-BA7F-4CDD-B6B4-44BBEC52BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE1C84D-1F87-4533-B217-64780FA4BAA6}">
   <dimension ref="A1:G728"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC Fittings PRICE.xlsx
+++ b/Side Bar Files/GWD Data/PVC Fittings PRICE.xlsx
@@ -1115,7 +1115,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEE1C84D-1F87-4533-B217-64780FA4BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C358C9A7-9CA3-4171-B35E-7C0EE57ABAA6}">
   <dimension ref="A1:G728"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
